--- a/CIS_Cassandra_Compliance_Report.xlsx
+++ b/CIS_Cassandra_Compliance_Report.xlsx
@@ -1366,9 +1366,9 @@
           <t>Configure vm.swappiness</t>
         </is>
       </c>
-      <c r="C27" s="5" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">60 </t>
+          <t xml:space="preserve">1 </t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -1386,11 +1386,7 @@
           <t xml:space="preserve">0 or 1 </t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">sysctl -w vm.swappiness=1 </t>
-        </is>
-      </c>
+      <c r="G27" s="2" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -1436,9 +1432,9 @@
           <t>Disable IPv6</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -1448,7 +1444,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 </t>
+          <t xml:space="preserve">1 </t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -1456,11 +1452,7 @@
           <t xml:space="preserve">1 </t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">sysctl -w net.ipv6.conf.all.disable_ipv6=1 </t>
-        </is>
-      </c>
+      <c r="G29" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2378,9 +2370,9 @@
           <t>Configure vm.swappiness</t>
         </is>
       </c>
-      <c r="C27" s="5" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -2390,7 +2382,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">60 </t>
+          <t xml:space="preserve">1 </t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -2398,11 +2390,7 @@
           <t xml:space="preserve">0 or 1 </t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">sysctl -w vm.swappiness=1 </t>
-        </is>
-      </c>
+      <c r="G27" s="2" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -2448,9 +2436,9 @@
           <t>Disable IPv6</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -2460,7 +2448,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 </t>
+          <t xml:space="preserve">1 </t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -2468,11 +2456,7 @@
           <t xml:space="preserve">1 </t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">sysctl -w net.ipv6.conf.all.disable_ipv6=1 </t>
-        </is>
-      </c>
+      <c r="G29" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3390,9 +3374,9 @@
           <t>Configure vm.swappiness</t>
         </is>
       </c>
-      <c r="C27" s="5" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -3402,7 +3386,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">60 </t>
+          <t xml:space="preserve">1 </t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -3410,11 +3394,7 @@
           <t xml:space="preserve">0 or 1 </t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">sysctl -w vm.swappiness=1 </t>
-        </is>
-      </c>
+      <c r="G27" s="2" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -3460,9 +3440,9 @@
           <t>Disable IPv6</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -3472,7 +3452,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 </t>
+          <t xml:space="preserve">1 </t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -3480,11 +3460,7 @@
           <t xml:space="preserve">1 </t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">sysctl -w net.ipv6.conf.all.disable_ipv6=1 </t>
-        </is>
-      </c>
+      <c r="G29" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
